--- a/youzi/轮回666/index.xlsx
+++ b/youzi/轮回666/index.xlsx
@@ -39,625 +39,643 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF5CACF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -675,24 +693,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
@@ -705,7 +717,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -723,24 +735,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
@@ -759,6 +753,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
@@ -766,12 +772,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2442,7 +2442,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -4321.62万</v>
       </c>
       <c r="E2">
@@ -2457,40 +2457,40 @@
       <c r="H2">
         <v>-8.93</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="12">
         <v>-1.16</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="3">
         <v>1.68</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="5">
         <v>3.44</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="4">
         <v>2.8</v>
       </c>
       <c r="M2" s="6">
         <v>8.43</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="9">
         <v>8.26</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="7">
         <v>1.85</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="13">
         <v>1.29</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="10">
         <v>6.24</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="1">
         <v>2.84</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="11">
         <v>4.86</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="8">
         <v>10.19</v>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       <c r="C3" t="str">
         <v>600250</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="16" t="str">
         <v>净买: 7132.41万</v>
       </c>
       <c r="E3">
@@ -2519,40 +2519,40 @@
       <c r="H3">
         <v>-1.63</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="24">
         <v>11.79</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="25">
         <v>22.97</v>
       </c>
       <c r="K3" s="17">
         <v>10.66</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="26">
         <v>4.1</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="20">
         <v>-0.44</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="14">
         <v>-3.41</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="18">
         <v>-6.38</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="21">
         <v>-7.69</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="19">
         <v>-6.64</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="15">
         <v>-6.72</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="22">
         <v>-6.81</v>
       </c>
-      <c r="T3" s="26">
+      <c r="T3" s="23">
         <v>0.52</v>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       <c r="C4" t="str">
         <v>001339</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -4.69万</v>
       </c>
       <c r="E4">
@@ -2581,40 +2581,40 @@
       <c r="H4">
         <v>4.9</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="31">
         <v>-2.37</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="32">
         <v>-5.33</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="37">
         <v>-8.23</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="33">
         <v>-8.82</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="38">
         <v>-8.07</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="34">
         <v>-5.42</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="29">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="30">
         <v>-7.04</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="35">
         <v>-9.46</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="36">
         <v>-8.86</v>
       </c>
       <c r="S4" s="28">
         <v>-9.81</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="39">
         <v>25.56</v>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       <c r="C5" t="str">
         <v>001339</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="44" t="str">
         <v>净卖: -7.88万</v>
       </c>
       <c r="E5">
@@ -2646,37 +2646,37 @@
       <c r="I5" s="40">
         <v>3.75</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="41">
         <v>0.58</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="51">
         <v>-0.08</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="45">
         <v>0.75</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="46">
         <v>3.65</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="52">
         <v>2.71</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="42">
         <v>1.88</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="47">
         <v>-0.77</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="48">
         <v>-0.12</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="49">
         <v>-1.15</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="50">
         <v>2.13</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="43">
         <v>37.61</v>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       <c r="C6" t="str">
         <v>603516</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="55" t="str">
         <v>净买: 5860.40万</v>
       </c>
       <c r="E6">
@@ -2708,37 +2708,37 @@
       <c r="I6" s="64">
         <v>9.46</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="65">
         <v>13.49</v>
       </c>
       <c r="K6" s="56">
         <v>20.29</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="53">
         <v>17.28</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="58">
         <v>29</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="61">
         <v>36.81</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="57">
         <v>45.23</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="54">
         <v>59.76</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="59">
         <v>43.78</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="62">
         <v>41.97</v>
       </c>
       <c r="S6" s="60">
         <v>40.57</v>
       </c>
-      <c r="T6" s="61">
+      <c r="T6" s="63">
         <v>85.75</v>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="70" t="str">
         <v>净买: 6772.87万</v>
       </c>
       <c r="E7">
@@ -2767,40 +2767,40 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="76">
         <v>6.4</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="77">
         <v>17.05</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="68">
         <v>5.34</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="78">
         <v>4.01</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="71">
         <v>2.98</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="72">
         <v>4.47</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="73">
         <v>7.94</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="69">
         <v>-2.85</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="74">
         <v>-1.92</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="75">
         <v>4.08</v>
       </c>
       <c r="S7" s="66">
         <v>-6.33</v>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="67">
         <v>36.09</v>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       <c r="C8" t="str">
         <v>000718</v>
       </c>
-      <c r="D8" s="83" t="str">
+      <c r="D8" s="85" t="str">
         <v>净买: 3497.63万</v>
       </c>
       <c r="E8">
@@ -2829,40 +2829,40 @@
       <c r="H8">
         <v>3.93</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="79">
         <v>2.33</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="80">
         <v>1.74</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="81">
         <v>-5.52</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="82">
         <v>-2.33</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="89">
         <v>-12.21</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="88">
         <v>-20.93</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="90">
         <v>-23.84</v>
       </c>
       <c r="P8" s="86">
         <v>-22.38</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="91">
         <v>-24.71</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="87">
         <v>-24.71</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="83">
         <v>-24.13</v>
       </c>
-      <c r="T8" s="87">
+      <c r="T8" s="84">
         <v>-38.08</v>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       <c r="C9" t="str">
         <v>002853</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="97" t="str">
         <v>净买: 1704.86万</v>
       </c>
       <c r="E9">
@@ -2891,40 +2891,40 @@
       <c r="H9">
         <v>-0.88</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="102">
         <v>9.12</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="98">
         <v>8.64</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="92">
         <v>12.55</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="93">
         <v>13.72</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="94">
         <v>11.34</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="103">
         <v>11.78</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="95">
         <v>10.65</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="104">
         <v>14</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="96">
         <v>25.42</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="99">
         <v>32.36</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="100">
         <v>29.18</v>
       </c>
-      <c r="T9" s="100">
+      <c r="T9" s="101">
         <v>4.72</v>
       </c>
     </row>
@@ -2987,40 +2987,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="109">
+      <c r="I11" s="110">
         <v>75</v>
       </c>
-      <c r="J11" s="113">
+      <c r="J11" s="115">
         <v>87.5</v>
       </c>
-      <c r="K11" s="110">
+      <c r="K11" s="116">
         <v>62.5</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="113">
         <v>75</v>
       </c>
-      <c r="M11" s="107">
+      <c r="M11" s="111">
         <v>62.5</v>
       </c>
-      <c r="N11" s="114">
+      <c r="N11" s="105">
         <v>62.5</v>
       </c>
-      <c r="O11" s="115">
+      <c r="O11" s="112">
         <v>62.5</v>
       </c>
-      <c r="P11" s="108">
+      <c r="P11" s="106">
         <v>37.5</v>
       </c>
-      <c r="Q11" s="112">
+      <c r="Q11" s="107">
         <v>37.5</v>
       </c>
-      <c r="R11" s="105">
+      <c r="R11" s="108">
         <v>50</v>
       </c>
-      <c r="S11" s="116">
+      <c r="S11" s="114">
         <v>50</v>
       </c>
-      <c r="T11" s="106">
+      <c r="T11" s="109">
         <v>87.5</v>
       </c>
     </row>
@@ -3035,40 +3035,40 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="125">
+      <c r="I12" s="118">
         <v>4.91</v>
       </c>
-      <c r="J12" s="126">
+      <c r="J12" s="125">
         <v>7.6</v>
       </c>
-      <c r="K12" s="127">
+      <c r="K12" s="128">
         <v>4.81</v>
       </c>
-      <c r="L12" s="118">
+      <c r="L12" s="117">
         <v>3.94</v>
       </c>
-      <c r="M12" s="120">
+      <c r="M12" s="123">
         <v>4.33</v>
       </c>
-      <c r="N12" s="122">
+      <c r="N12" s="119">
         <v>4.28</v>
       </c>
-      <c r="O12" s="123">
+      <c r="O12" s="120">
         <v>3.88</v>
       </c>
-      <c r="P12" s="124">
+      <c r="P12" s="126">
         <v>4.29</v>
       </c>
-      <c r="Q12" s="128">
+      <c r="Q12" s="121">
         <v>4.07</v>
       </c>
-      <c r="R12" s="117">
+      <c r="R12" s="124">
         <v>4.98</v>
       </c>
-      <c r="S12" s="121">
+      <c r="S12" s="122">
         <v>3.71</v>
       </c>
-      <c r="T12" s="119">
+      <c r="T12" s="127">
         <v>20.29</v>
       </c>
     </row>

--- a/youzi/轮回666/index.xlsx
+++ b/youzi/轮回666/index.xlsx
@@ -39,12 +39,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEB8C95"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -57,37 +81,583 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,559 +669,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -669,13 +705,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -705,31 +735,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -753,49 +777,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAA1E2B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2442,7 +2442,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -4321.62万</v>
       </c>
       <c r="E2">
@@ -2457,40 +2457,40 @@
       <c r="H2">
         <v>-8.93</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>-1.16</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="7">
         <v>1.68</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="8">
         <v>3.44</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="13">
         <v>2.8</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="9">
         <v>8.43</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="10">
         <v>8.26</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="4">
         <v>1.85</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="1">
         <v>1.29</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="5">
         <v>6.24</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <v>2.84</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="12">
         <v>4.86</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="3">
         <v>10.19</v>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       <c r="C3" t="str">
         <v>600250</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="19" t="str">
         <v>净买: 7132.41万</v>
       </c>
       <c r="E3">
@@ -2519,40 +2519,40 @@
       <c r="H3">
         <v>-1.63</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="15">
         <v>11.79</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="16">
         <v>22.97</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="24">
         <v>10.66</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="25">
         <v>4.1</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="23">
         <v>-0.44</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="20">
         <v>-3.41</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="17">
         <v>-6.38</v>
       </c>
       <c r="P3" s="21">
         <v>-7.69</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="18">
         <v>-6.64</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="26">
         <v>-6.72</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="14">
         <v>-6.81</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="22">
         <v>0.52</v>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       <c r="C4" t="str">
         <v>001339</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="33" t="str">
         <v>净卖: -4.69万</v>
       </c>
       <c r="E4">
@@ -2581,37 +2581,37 @@
       <c r="H4">
         <v>4.9</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="27">
         <v>-2.37</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="28">
         <v>-5.33</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="29">
         <v>-8.23</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="34">
         <v>-8.82</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="30">
         <v>-8.07</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="35">
         <v>-5.42</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="32">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="36">
         <v>-7.04</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="37">
         <v>-9.46</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="31">
         <v>-8.86</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="38">
         <v>-9.81</v>
       </c>
       <c r="T4" s="39">
@@ -2628,7 +2628,7 @@
       <c r="C5" t="str">
         <v>001339</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="50" t="str">
         <v>净卖: -7.88万</v>
       </c>
       <c r="E5">
@@ -2643,40 +2643,40 @@
       <c r="H5">
         <v>-6.54</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="41">
         <v>3.75</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="51">
         <v>0.58</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="42">
         <v>-0.08</v>
       </c>
       <c r="L5" s="45">
         <v>0.75</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="52">
         <v>3.65</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="40">
         <v>2.71</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="46">
         <v>1.88</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="43">
         <v>-0.77</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="47">
         <v>-0.12</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="44">
         <v>-1.15</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="48">
         <v>2.13</v>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="49">
         <v>37.61</v>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       <c r="C6" t="str">
         <v>603516</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="64" t="str">
         <v>净买: 5860.40万</v>
       </c>
       <c r="E6">
@@ -2705,40 +2705,40 @@
       <c r="H6">
         <v>0.49</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="56">
         <v>9.46</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="57">
         <v>13.49</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="58">
         <v>20.29</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="65">
         <v>17.28</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="53">
         <v>29</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="60">
         <v>36.81</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="54">
         <v>45.23</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="61">
         <v>59.76</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="62">
         <v>43.78</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="55">
         <v>41.97</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="63">
         <v>40.57</v>
       </c>
-      <c r="T6" s="63">
+      <c r="T6" s="59">
         <v>85.75</v>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="75" t="str">
         <v>净买: 6772.87万</v>
       </c>
       <c r="E7">
@@ -2767,40 +2767,40 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="70">
         <v>6.4</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="71">
         <v>17.05</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="67">
         <v>5.34</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="72">
         <v>4.01</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="73">
         <v>2.98</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="76">
         <v>4.47</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="77">
         <v>7.94</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="78">
         <v>-2.85</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="68">
         <v>-1.92</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="66">
         <v>4.08</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="74">
         <v>-6.33</v>
       </c>
-      <c r="T7" s="67">
+      <c r="T7" s="69">
         <v>36.09</v>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       <c r="C8" t="str">
         <v>000718</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="90" t="str">
         <v>净买: 3497.63万</v>
       </c>
       <c r="E8">
@@ -2829,40 +2829,40 @@
       <c r="H8">
         <v>3.93</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="88">
         <v>2.33</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="91">
         <v>1.74</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="79">
         <v>-5.52</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="89">
         <v>-2.33</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="86">
         <v>-12.21</v>
       </c>
-      <c r="N8" s="88">
+      <c r="N8" s="87">
         <v>-20.93</v>
       </c>
-      <c r="O8" s="90">
+      <c r="O8" s="80">
         <v>-23.84</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="82">
         <v>-22.38</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="83">
         <v>-24.71</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="81">
         <v>-24.71</v>
       </c>
-      <c r="S8" s="83">
+      <c r="S8" s="84">
         <v>-24.13</v>
       </c>
-      <c r="T8" s="84">
+      <c r="T8" s="85">
         <v>-38.08</v>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       <c r="C9" t="str">
         <v>002853</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="101" t="str">
         <v>净买: 1704.86万</v>
       </c>
       <c r="E9">
@@ -2891,31 +2891,31 @@
       <c r="H9">
         <v>-0.88</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="96">
         <v>9.12</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="97">
         <v>8.64</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="104">
         <v>12.55</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="102">
         <v>13.72</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="103">
         <v>11.34</v>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="98">
         <v>11.78</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="93">
         <v>10.65</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="94">
         <v>14</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="92">
         <v>25.42</v>
       </c>
       <c r="R9" s="99">
@@ -2924,7 +2924,7 @@
       <c r="S9" s="100">
         <v>29.18</v>
       </c>
-      <c r="T9" s="101">
+      <c r="T9" s="95">
         <v>4.72</v>
       </c>
     </row>
@@ -2987,40 +2987,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="110">
+      <c r="I11" s="107">
         <v>75</v>
       </c>
-      <c r="J11" s="115">
+      <c r="J11" s="110">
         <v>87.5</v>
       </c>
-      <c r="K11" s="116">
+      <c r="K11" s="111">
         <v>62.5</v>
       </c>
-      <c r="L11" s="113">
+      <c r="L11" s="115">
         <v>75</v>
       </c>
-      <c r="M11" s="111">
+      <c r="M11" s="112">
         <v>62.5</v>
       </c>
-      <c r="N11" s="105">
+      <c r="N11" s="116">
         <v>62.5</v>
       </c>
-      <c r="O11" s="112">
+      <c r="O11" s="105">
         <v>62.5</v>
       </c>
-      <c r="P11" s="106">
+      <c r="P11" s="108">
         <v>37.5</v>
       </c>
-      <c r="Q11" s="107">
+      <c r="Q11" s="109">
         <v>37.5</v>
       </c>
-      <c r="R11" s="108">
+      <c r="R11" s="106">
         <v>50</v>
       </c>
-      <c r="S11" s="114">
+      <c r="S11" s="113">
         <v>50</v>
       </c>
-      <c r="T11" s="109">
+      <c r="T11" s="114">
         <v>87.5</v>
       </c>
     </row>
@@ -3035,40 +3035,40 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="118">
+      <c r="I12" s="123">
         <v>4.91</v>
       </c>
-      <c r="J12" s="125">
+      <c r="J12" s="124">
         <v>7.6</v>
       </c>
-      <c r="K12" s="128">
+      <c r="K12" s="125">
         <v>4.81</v>
       </c>
-      <c r="L12" s="117">
+      <c r="L12" s="121">
         <v>3.94</v>
       </c>
-      <c r="M12" s="123">
+      <c r="M12" s="122">
         <v>4.33</v>
       </c>
-      <c r="N12" s="119">
+      <c r="N12" s="128">
         <v>4.28</v>
       </c>
-      <c r="O12" s="120">
+      <c r="O12" s="126">
         <v>3.88</v>
       </c>
-      <c r="P12" s="126">
+      <c r="P12" s="117">
         <v>4.29</v>
       </c>
-      <c r="Q12" s="121">
+      <c r="Q12" s="118">
         <v>4.07</v>
       </c>
-      <c r="R12" s="124">
+      <c r="R12" s="119">
         <v>4.98</v>
       </c>
-      <c r="S12" s="122">
+      <c r="S12" s="127">
         <v>3.71</v>
       </c>
-      <c r="T12" s="127">
+      <c r="T12" s="120">
         <v>20.29</v>
       </c>
     </row>

--- a/youzi/轮回666/index.xlsx
+++ b/youzi/轮回666/index.xlsx
@@ -39,25 +39,625 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF5CACF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,595 +669,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -669,6 +699,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -681,61 +723,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -766,36 +796,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2457,41 +2457,41 @@
       <c r="H2">
         <v>-8.93</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="7">
         <v>-1.16</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="12">
         <v>1.68</v>
       </c>
       <c r="K2" s="8">
         <v>3.44</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="9">
         <v>2.8</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="13">
         <v>8.43</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="1">
         <v>8.26</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="10">
         <v>1.85</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="11">
         <v>1.29</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="3">
         <v>6.24</v>
       </c>
       <c r="R2" s="2">
         <v>2.84</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="4">
         <v>4.86</v>
       </c>
-      <c r="T2" s="3">
-        <v>10.19</v>
+      <c r="T2" s="5">
+        <v>12.69</v>
       </c>
     </row>
     <row r="3">
@@ -2504,7 +2504,7 @@
       <c r="C3" t="str">
         <v>600250</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="21" t="str">
         <v>净买: 7132.41万</v>
       </c>
       <c r="E3">
@@ -2519,41 +2519,41 @@
       <c r="H3">
         <v>-1.63</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="22">
         <v>11.79</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="25">
         <v>22.97</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="26">
         <v>10.66</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="14">
         <v>4.1</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="15">
         <v>-0.44</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="16">
         <v>-3.41</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="18">
         <v>-6.38</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="17">
         <v>-7.69</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="23">
         <v>-6.64</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="19">
         <v>-6.72</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="24">
         <v>-6.81</v>
       </c>
-      <c r="T3" s="22">
-        <v>0.52</v>
+      <c r="T3" s="20">
+        <v>2.01</v>
       </c>
     </row>
     <row r="4">
@@ -2566,7 +2566,7 @@
       <c r="C4" t="str">
         <v>001339</v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -4.69万</v>
       </c>
       <c r="E4">
@@ -2581,41 +2581,41 @@
       <c r="H4">
         <v>4.9</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="34">
         <v>-2.37</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="35">
         <v>-5.33</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="37">
         <v>-8.23</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="29">
         <v>-8.82</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="36">
         <v>-8.07</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="38">
         <v>-5.42</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="30">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="31">
         <v>-7.04</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="27">
         <v>-9.46</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="32">
         <v>-8.86</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="28">
         <v>-9.81</v>
       </c>
-      <c r="T4" s="39">
-        <v>25.56</v>
+      <c r="T4" s="33">
+        <v>24.95</v>
       </c>
     </row>
     <row r="5">
@@ -2628,7 +2628,7 @@
       <c r="C5" t="str">
         <v>001339</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="49" t="str">
         <v>净卖: -7.88万</v>
       </c>
       <c r="E5">
@@ -2643,41 +2643,41 @@
       <c r="H5">
         <v>-6.54</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="50">
         <v>3.75</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="40">
         <v>0.58</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="41">
         <v>-0.08</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="42">
         <v>0.75</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="43">
         <v>3.65</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="44">
         <v>2.71</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="51">
         <v>1.88</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="46">
         <v>-0.77</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="52">
         <v>-0.12</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="45">
         <v>-1.15</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="47">
         <v>2.13</v>
       </c>
-      <c r="T5" s="49">
-        <v>37.61</v>
+      <c r="T5" s="48">
+        <v>36.94</v>
       </c>
     </row>
     <row r="6">
@@ -2690,7 +2690,7 @@
       <c r="C6" t="str">
         <v>603516</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="60" t="str">
         <v>净买: 5860.40万</v>
       </c>
       <c r="E6">
@@ -2705,41 +2705,41 @@
       <c r="H6">
         <v>0.49</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="65">
         <v>9.46</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="64">
         <v>13.49</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="53">
         <v>20.29</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="56">
         <v>17.28</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="61">
         <v>29</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="62">
         <v>36.81</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="57">
         <v>45.23</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="54">
         <v>59.76</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="63">
         <v>43.78</v>
       </c>
       <c r="R6" s="55">
         <v>41.97</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="58">
         <v>40.57</v>
       </c>
       <c r="T6" s="59">
-        <v>85.75</v>
+        <v>88.59</v>
       </c>
     </row>
     <row r="7">
@@ -2752,7 +2752,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="72" t="str">
         <v>净买: 6772.87万</v>
       </c>
       <c r="E7">
@@ -2767,41 +2767,41 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="69">
         <v>6.4</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="66">
         <v>17.05</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="73">
         <v>5.34</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="67">
         <v>4.01</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="74">
         <v>2.98</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="70">
         <v>4.47</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="71">
         <v>7.94</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="75">
         <v>-2.85</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="76">
         <v>-1.92</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="77">
         <v>4.08</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="78">
         <v>-6.33</v>
       </c>
-      <c r="T7" s="69">
-        <v>36.09</v>
+      <c r="T7" s="68">
+        <v>38.17</v>
       </c>
     </row>
     <row r="8">
@@ -2814,7 +2814,7 @@
       <c r="C8" t="str">
         <v>000718</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="89" t="str">
         <v>净买: 3497.63万</v>
       </c>
       <c r="E8">
@@ -2829,41 +2829,41 @@
       <c r="H8">
         <v>3.93</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="82">
         <v>2.33</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="90">
         <v>1.74</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="91">
         <v>-5.52</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="80">
         <v>-2.33</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="87">
         <v>-12.21</v>
       </c>
-      <c r="N8" s="87">
+      <c r="N8" s="83">
         <v>-20.93</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="84">
         <v>-23.84</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="81">
         <v>-22.38</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="88">
         <v>-24.71</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="85">
         <v>-24.71</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="79">
         <v>-24.13</v>
       </c>
-      <c r="T8" s="85">
-        <v>-38.08</v>
+      <c r="T8" s="86">
+        <v>-38.37</v>
       </c>
     </row>
     <row r="9">
@@ -2876,7 +2876,7 @@
       <c r="C9" t="str">
         <v>002853</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="97" t="str">
         <v>净买: 1704.86万</v>
       </c>
       <c r="E9">
@@ -2891,41 +2891,41 @@
       <c r="H9">
         <v>-0.88</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="98">
         <v>9.12</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="103">
         <v>8.64</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="102">
         <v>12.55</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="104">
         <v>13.72</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="99">
         <v>11.34</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="92">
         <v>11.78</v>
       </c>
-      <c r="O9" s="93">
+      <c r="O9" s="94">
         <v>10.65</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="95">
         <v>14</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="Q9" s="93">
         <v>25.42</v>
       </c>
-      <c r="R9" s="99">
+      <c r="R9" s="100">
         <v>32.36</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="101">
         <v>29.18</v>
       </c>
-      <c r="T9" s="95">
-        <v>4.72</v>
+      <c r="T9" s="96">
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -2987,40 +2987,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="107">
+      <c r="I11" s="114">
         <v>75</v>
       </c>
-      <c r="J11" s="110">
+      <c r="J11" s="115">
         <v>87.5</v>
       </c>
-      <c r="K11" s="111">
+      <c r="K11" s="110">
         <v>62.5</v>
       </c>
-      <c r="L11" s="115">
+      <c r="L11" s="116">
         <v>75</v>
       </c>
-      <c r="M11" s="112">
+      <c r="M11" s="111">
         <v>62.5</v>
       </c>
-      <c r="N11" s="116">
+      <c r="N11" s="112">
         <v>62.5</v>
       </c>
       <c r="O11" s="105">
         <v>62.5</v>
       </c>
-      <c r="P11" s="108">
+      <c r="P11" s="106">
         <v>37.5</v>
       </c>
       <c r="Q11" s="109">
         <v>37.5</v>
       </c>
-      <c r="R11" s="106">
+      <c r="R11" s="107">
         <v>50</v>
       </c>
       <c r="S11" s="113">
         <v>50</v>
       </c>
-      <c r="T11" s="114">
+      <c r="T11" s="108">
         <v>87.5</v>
       </c>
     </row>
@@ -3035,41 +3035,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="123">
+      <c r="I12" s="125">
         <v>4.91</v>
       </c>
-      <c r="J12" s="124">
+      <c r="J12" s="119">
         <v>7.6</v>
       </c>
-      <c r="K12" s="125">
+      <c r="K12" s="128">
         <v>4.81</v>
       </c>
-      <c r="L12" s="121">
+      <c r="L12" s="126">
         <v>3.94</v>
       </c>
-      <c r="M12" s="122">
+      <c r="M12" s="127">
         <v>4.33</v>
       </c>
-      <c r="N12" s="128">
+      <c r="N12" s="120">
         <v>4.28</v>
       </c>
-      <c r="O12" s="126">
+      <c r="O12" s="122">
         <v>3.88</v>
       </c>
-      <c r="P12" s="117">
+      <c r="P12" s="121">
         <v>4.29</v>
       </c>
-      <c r="Q12" s="118">
+      <c r="Q12" s="117">
         <v>4.07</v>
       </c>
-      <c r="R12" s="119">
+      <c r="R12" s="123">
         <v>4.98</v>
       </c>
-      <c r="S12" s="127">
+      <c r="S12" s="118">
         <v>3.71</v>
       </c>
-      <c r="T12" s="120">
-        <v>20.29</v>
+      <c r="T12" s="124">
+        <v>21.44</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/轮回666/index.xlsx
+++ b/youzi/轮回666/index.xlsx
@@ -45,685 +45,697 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEB8C95"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -753,18 +765,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAA1E2B"/>
         <bgColor/>
       </patternFill>
@@ -789,7 +789,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2442,7 +2442,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -4321.62万</v>
       </c>
       <c r="E2">
@@ -2457,41 +2457,41 @@
       <c r="H2">
         <v>-8.93</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>-1.16</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="6">
         <v>1.68</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="11">
         <v>3.44</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="10">
         <v>2.8</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="12">
         <v>8.43</v>
       </c>
       <c r="N2" s="1">
         <v>8.26</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="7">
         <v>1.85</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="2">
         <v>1.29</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="8">
         <v>6.24</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="13">
         <v>2.84</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="9">
         <v>4.86</v>
       </c>
-      <c r="T2" s="5">
-        <v>12.69</v>
+      <c r="T2" s="3">
+        <v>11.83</v>
       </c>
     </row>
     <row r="3">
@@ -2522,38 +2522,38 @@
       <c r="I3" s="22">
         <v>11.79</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="15">
         <v>22.97</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="25">
         <v>10.66</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="26">
         <v>4.1</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="16">
         <v>-0.44</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="14">
         <v>-3.41</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="23">
         <v>-6.38</v>
       </c>
       <c r="P3" s="17">
         <v>-7.69</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="24">
         <v>-6.64</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="18">
         <v>-6.72</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="20">
         <v>-6.81</v>
       </c>
-      <c r="T3" s="20">
-        <v>2.01</v>
+      <c r="T3" s="19">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="4">
@@ -2566,7 +2566,7 @@
       <c r="C4" t="str">
         <v>001339</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="32" t="str">
         <v>净卖: -4.69万</v>
       </c>
       <c r="E4">
@@ -2581,41 +2581,41 @@
       <c r="H4">
         <v>4.9</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="33">
         <v>-2.37</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="30">
         <v>-5.33</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="28">
         <v>-8.23</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="36">
         <v>-8.82</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="34">
         <v>-8.07</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="37">
         <v>-5.42</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="35">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="38">
         <v>-7.04</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="39">
         <v>-9.46</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="27">
         <v>-8.86</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="29">
         <v>-9.81</v>
       </c>
-      <c r="T4" s="33">
-        <v>24.95</v>
+      <c r="T4" s="31">
+        <v>26.47</v>
       </c>
     </row>
     <row r="5">
@@ -2628,7 +2628,7 @@
       <c r="C5" t="str">
         <v>001339</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -7.88万</v>
       </c>
       <c r="E5">
@@ -2643,41 +2643,41 @@
       <c r="H5">
         <v>-6.54</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="46">
         <v>3.75</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="52">
         <v>0.58</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="47">
         <v>-0.08</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="40">
         <v>0.75</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="48">
         <v>3.65</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="49">
         <v>2.71</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="41">
         <v>1.88</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="42">
         <v>-0.77</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="43">
         <v>-0.12</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="44">
         <v>-1.15</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="50">
         <v>2.13</v>
       </c>
-      <c r="T5" s="48">
-        <v>36.94</v>
+      <c r="T5" s="51">
+        <v>38.61</v>
       </c>
     </row>
     <row r="6">
@@ -2690,7 +2690,7 @@
       <c r="C6" t="str">
         <v>603516</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="64" t="str">
         <v>净买: 5860.40万</v>
       </c>
       <c r="E6">
@@ -2708,38 +2708,38 @@
       <c r="I6" s="65">
         <v>9.46</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="53">
         <v>13.49</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="54">
         <v>20.29</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="55">
         <v>17.28</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="60">
         <v>29</v>
       </c>
       <c r="N6" s="62">
         <v>36.81</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="63">
         <v>45.23</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="58">
         <v>59.76</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="56">
         <v>43.78</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="57">
         <v>41.97</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="59">
         <v>40.57</v>
       </c>
-      <c r="T6" s="59">
-        <v>88.59</v>
+      <c r="T6" s="61">
+        <v>85.37</v>
       </c>
     </row>
     <row r="7">
@@ -2752,7 +2752,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="72" t="str">
+      <c r="D7" s="75" t="str">
         <v>净买: 6772.87万</v>
       </c>
       <c r="E7">
@@ -2767,41 +2767,41 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="66">
         <v>6.4</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="67">
         <v>17.05</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="69">
         <v>5.34</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="76">
         <v>4.01</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="72">
         <v>2.98</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="68">
         <v>4.47</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="70">
         <v>7.94</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="73">
         <v>-2.85</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="77">
         <v>-1.92</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="74">
         <v>4.08</v>
       </c>
       <c r="S7" s="78">
         <v>-6.33</v>
       </c>
-      <c r="T7" s="68">
-        <v>38.17</v>
+      <c r="T7" s="71">
+        <v>35.81</v>
       </c>
     </row>
     <row r="8">
@@ -2814,7 +2814,7 @@
       <c r="C8" t="str">
         <v>000718</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="88" t="str">
         <v>净买: 3497.63万</v>
       </c>
       <c r="E8">
@@ -2829,41 +2829,41 @@
       <c r="H8">
         <v>3.93</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="84">
         <v>2.33</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="82">
         <v>1.74</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="89">
         <v>-5.52</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="86">
         <v>-2.33</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="90">
         <v>-12.21</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="91">
         <v>-20.93</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="85">
         <v>-23.84</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="79">
         <v>-22.38</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="80">
         <v>-24.71</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="81">
         <v>-24.71</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="87">
         <v>-24.13</v>
       </c>
-      <c r="T8" s="86">
-        <v>-38.37</v>
+      <c r="T8" s="83">
+        <v>-38.66</v>
       </c>
     </row>
     <row r="9">
@@ -2891,41 +2891,41 @@
       <c r="H9">
         <v>-0.88</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="102">
         <v>9.12</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="98">
         <v>8.64</v>
       </c>
-      <c r="K9" s="102">
+      <c r="K9" s="99">
         <v>12.55</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="94">
         <v>13.72</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="100">
         <v>11.34</v>
       </c>
-      <c r="N9" s="92">
+      <c r="N9" s="103">
         <v>11.78</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="95">
         <v>10.65</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="96">
         <v>14</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="104">
         <v>25.42</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="92">
         <v>32.36</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="93">
         <v>29.18</v>
       </c>
-      <c r="T9" s="96">
-        <v>6.5</v>
+      <c r="T9" s="101">
+        <v>17.15</v>
       </c>
     </row>
     <row r="10">
@@ -2993,35 +2993,35 @@
       <c r="J11" s="115">
         <v>87.5</v>
       </c>
-      <c r="K11" s="110">
+      <c r="K11" s="107">
         <v>62.5</v>
       </c>
-      <c r="L11" s="116">
+      <c r="L11" s="111">
         <v>75</v>
       </c>
-      <c r="M11" s="111">
+      <c r="M11" s="112">
         <v>62.5</v>
       </c>
-      <c r="N11" s="112">
+      <c r="N11" s="108">
         <v>62.5</v>
       </c>
-      <c r="O11" s="105">
+      <c r="O11" s="110">
         <v>62.5</v>
       </c>
-      <c r="P11" s="106">
+      <c r="P11" s="116">
         <v>37.5</v>
       </c>
-      <c r="Q11" s="109">
+      <c r="Q11" s="105">
         <v>37.5</v>
       </c>
-      <c r="R11" s="107">
+      <c r="R11" s="109">
         <v>50</v>
       </c>
-      <c r="S11" s="113">
+      <c r="S11" s="106">
         <v>50</v>
       </c>
-      <c r="T11" s="108">
-        <v>87.5</v>
+      <c r="T11" s="113">
+        <v>75</v>
       </c>
     </row>
     <row r="12">
@@ -3035,41 +3035,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="125">
+      <c r="I12" s="124">
         <v>4.91</v>
       </c>
-      <c r="J12" s="119">
+      <c r="J12" s="121">
         <v>7.6</v>
       </c>
-      <c r="K12" s="128">
+      <c r="K12" s="125">
         <v>4.81</v>
       </c>
-      <c r="L12" s="126">
+      <c r="L12" s="117">
         <v>3.94</v>
       </c>
-      <c r="M12" s="127">
+      <c r="M12" s="118">
         <v>4.33</v>
       </c>
-      <c r="N12" s="120">
+      <c r="N12" s="126">
         <v>4.28</v>
       </c>
       <c r="O12" s="122">
         <v>3.88</v>
       </c>
-      <c r="P12" s="121">
+      <c r="P12" s="128">
         <v>4.29</v>
       </c>
-      <c r="Q12" s="117">
+      <c r="Q12" s="127">
         <v>4.07</v>
       </c>
-      <c r="R12" s="123">
+      <c r="R12" s="119">
         <v>4.98</v>
       </c>
-      <c r="S12" s="118">
+      <c r="S12" s="120">
         <v>3.71</v>
       </c>
-      <c r="T12" s="124">
-        <v>21.44</v>
+      <c r="T12" s="123">
+        <v>21.99</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/轮回666/index.xlsx
+++ b/youzi/轮回666/index.xlsx
@@ -39,6 +39,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB92533"/>
         <bgColor/>
       </patternFill>
@@ -51,6 +93,150 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF52B869"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -63,19 +249,421 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,582 +675,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
@@ -675,6 +687,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
@@ -687,12 +705,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
@@ -705,103 +717,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2442,7 +2442,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="5" t="str">
         <v>净卖: -4321.62万</v>
       </c>
       <c r="E2">
@@ -2457,41 +2457,41 @@
       <c r="H2">
         <v>-8.93</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="11">
         <v>-1.16</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="12">
         <v>1.68</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="6">
         <v>3.44</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="13">
         <v>2.8</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="7">
         <v>8.43</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="8">
         <v>8.26</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="2">
         <v>1.85</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="9">
         <v>1.29</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="1">
         <v>6.24</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="10">
         <v>2.84</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="3">
         <v>4.86</v>
       </c>
-      <c r="T2" s="3">
-        <v>11.83</v>
+      <c r="T2" s="4">
+        <v>1.59</v>
       </c>
     </row>
     <row r="3">
@@ -2504,7 +2504,7 @@
       <c r="C3" t="str">
         <v>600250</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="23" t="str">
         <v>净买: 7132.41万</v>
       </c>
       <c r="E3">
@@ -2519,41 +2519,41 @@
       <c r="H3">
         <v>-1.63</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="20">
         <v>11.79</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="24">
         <v>22.97</v>
       </c>
       <c r="K3" s="25">
         <v>10.66</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="21">
         <v>4.1</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="26">
         <v>-0.44</v>
       </c>
       <c r="N3" s="14">
         <v>-3.41</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="15">
         <v>-6.38</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="16">
         <v>-7.69</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="17">
         <v>-6.64</v>
       </c>
       <c r="R3" s="18">
         <v>-6.72</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="19">
         <v>-6.81</v>
       </c>
-      <c r="T3" s="19">
-        <v>-0.7</v>
+      <c r="T3" s="22">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="4">
@@ -2566,7 +2566,7 @@
       <c r="C4" t="str">
         <v>001339</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -4.69万</v>
       </c>
       <c r="E4">
@@ -2581,41 +2581,41 @@
       <c r="H4">
         <v>4.9</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="31">
         <v>-2.37</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="36">
         <v>-5.33</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="39">
         <v>-8.23</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="28">
         <v>-8.82</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="32">
         <v>-8.07</v>
       </c>
       <c r="N4" s="37">
         <v>-5.42</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="33">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="27">
         <v>-7.04</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="29">
         <v>-9.46</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="38">
         <v>-8.86</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="30">
         <v>-9.81</v>
       </c>
-      <c r="T4" s="31">
-        <v>26.47</v>
+      <c r="T4" s="34">
+        <v>41.65</v>
       </c>
     </row>
     <row r="5">
@@ -2628,7 +2628,7 @@
       <c r="C5" t="str">
         <v>001339</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="47" t="str">
         <v>净卖: -7.88万</v>
       </c>
       <c r="E5">
@@ -2643,41 +2643,41 @@
       <c r="H5">
         <v>-6.54</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="48">
         <v>3.75</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="44">
         <v>0.58</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="52">
         <v>-0.08</v>
       </c>
       <c r="L5" s="40">
         <v>0.75</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="49">
         <v>3.65</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="50">
         <v>2.71</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="45">
         <v>1.88</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="41">
         <v>-0.77</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="51">
         <v>-0.12</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="42">
         <v>-1.15</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="46">
         <v>2.13</v>
       </c>
-      <c r="T5" s="51">
-        <v>38.61</v>
+      <c r="T5" s="43">
+        <v>55.24</v>
       </c>
     </row>
     <row r="6">
@@ -2690,7 +2690,7 @@
       <c r="C6" t="str">
         <v>603516</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="61" t="str">
         <v>净买: 5860.40万</v>
       </c>
       <c r="E6">
@@ -2711,35 +2711,35 @@
       <c r="J6" s="53">
         <v>13.49</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="59">
         <v>20.29</v>
       </c>
       <c r="L6" s="55">
         <v>17.28</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="56">
         <v>29</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="54">
         <v>36.81</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="57">
         <v>45.23</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="60">
         <v>59.76</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="58">
         <v>43.78</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="62">
         <v>41.97</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="63">
         <v>40.57</v>
       </c>
-      <c r="T6" s="61">
-        <v>85.37</v>
+      <c r="T6" s="64">
+        <v>84.19</v>
       </c>
     </row>
     <row r="7">
@@ -2752,7 +2752,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="74" t="str">
         <v>净买: 6772.87万</v>
       </c>
       <c r="E7">
@@ -2770,38 +2770,38 @@
       <c r="I7" s="66">
         <v>6.4</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="75">
         <v>17.05</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="70">
         <v>5.34</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="71">
         <v>4.01</v>
       </c>
       <c r="M7" s="72">
         <v>2.98</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="73">
         <v>4.47</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="76">
         <v>7.94</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="77">
         <v>-2.85</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="67">
         <v>-1.92</v>
       </c>
-      <c r="R7" s="74">
+      <c r="R7" s="68">
         <v>4.08</v>
       </c>
       <c r="S7" s="78">
         <v>-6.33</v>
       </c>
-      <c r="T7" s="71">
-        <v>35.81</v>
+      <c r="T7" s="69">
+        <v>34.94</v>
       </c>
     </row>
     <row r="8">
@@ -2814,7 +2814,7 @@
       <c r="C8" t="str">
         <v>000718</v>
       </c>
-      <c r="D8" s="88" t="str">
+      <c r="D8" s="80" t="str">
         <v>净买: 3497.63万</v>
       </c>
       <c r="E8">
@@ -2829,41 +2829,41 @@
       <c r="H8">
         <v>3.93</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="86">
         <v>2.33</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="81">
         <v>1.74</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="90">
         <v>-5.52</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="84">
         <v>-2.33</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="87">
         <v>-12.21</v>
       </c>
-      <c r="N8" s="91">
+      <c r="N8" s="88">
         <v>-20.93</v>
       </c>
       <c r="O8" s="85">
         <v>-23.84</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="82">
         <v>-22.38</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="91">
         <v>-24.71</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="89">
         <v>-24.71</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="79">
         <v>-24.13</v>
       </c>
       <c r="T8" s="83">
-        <v>-38.66</v>
+        <v>-39.83</v>
       </c>
     </row>
     <row r="9">
@@ -2876,7 +2876,7 @@
       <c r="C9" t="str">
         <v>002853</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="100" t="str">
         <v>净买: 1704.86万</v>
       </c>
       <c r="E9">
@@ -2891,41 +2891,41 @@
       <c r="H9">
         <v>-0.88</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="92">
         <v>9.12</v>
       </c>
       <c r="J9" s="98">
         <v>8.64</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="93">
         <v>12.55</v>
       </c>
       <c r="L9" s="94">
         <v>13.72</v>
       </c>
-      <c r="M9" s="100">
+      <c r="M9" s="101">
         <v>11.34</v>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="102">
         <v>11.78</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="103">
         <v>10.65</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="99">
         <v>14</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="95">
         <v>25.42</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="96">
         <v>32.36</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="97">
         <v>29.18</v>
       </c>
-      <c r="T9" s="101">
-        <v>17.15</v>
+      <c r="T9" s="104">
+        <v>4.8</v>
       </c>
     </row>
     <row r="10">
@@ -2987,40 +2987,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="114">
+      <c r="I11" s="113">
         <v>75</v>
       </c>
-      <c r="J11" s="115">
+      <c r="J11" s="116">
         <v>87.5</v>
       </c>
-      <c r="K11" s="107">
+      <c r="K11" s="112">
         <v>62.5</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="105">
         <v>75</v>
       </c>
-      <c r="M11" s="112">
+      <c r="M11" s="110">
         <v>62.5</v>
       </c>
-      <c r="N11" s="108">
+      <c r="N11" s="106">
         <v>62.5</v>
       </c>
-      <c r="O11" s="110">
+      <c r="O11" s="111">
         <v>62.5</v>
       </c>
-      <c r="P11" s="116">
+      <c r="P11" s="107">
         <v>37.5</v>
       </c>
-      <c r="Q11" s="105">
+      <c r="Q11" s="114">
         <v>37.5</v>
       </c>
-      <c r="R11" s="109">
+      <c r="R11" s="108">
         <v>50</v>
       </c>
-      <c r="S11" s="106">
+      <c r="S11" s="109">
         <v>50</v>
       </c>
-      <c r="T11" s="113">
+      <c r="T11" s="115">
         <v>75</v>
       </c>
     </row>
@@ -3035,41 +3035,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="124">
+      <c r="I12" s="120">
         <v>4.91</v>
       </c>
       <c r="J12" s="121">
         <v>7.6</v>
       </c>
-      <c r="K12" s="125">
+      <c r="K12" s="118">
         <v>4.81</v>
       </c>
-      <c r="L12" s="117">
+      <c r="L12" s="128">
         <v>3.94</v>
       </c>
-      <c r="M12" s="118">
+      <c r="M12" s="123">
         <v>4.33</v>
       </c>
-      <c r="N12" s="126">
+      <c r="N12" s="124">
         <v>4.28</v>
       </c>
       <c r="O12" s="122">
         <v>3.88</v>
       </c>
-      <c r="P12" s="128">
+      <c r="P12" s="125">
         <v>4.29</v>
       </c>
-      <c r="Q12" s="127">
+      <c r="Q12" s="117">
         <v>4.07</v>
       </c>
-      <c r="R12" s="119">
+      <c r="R12" s="126">
         <v>4.98</v>
       </c>
-      <c r="S12" s="120">
+      <c r="S12" s="127">
         <v>3.71</v>
       </c>
-      <c r="T12" s="123">
-        <v>21.99</v>
+      <c r="T12" s="119">
+        <v>22.32</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/轮回666/index.xlsx
+++ b/youzi/轮回666/index.xlsx
@@ -39,25 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
+        <fgColor rgb="FFEB8C95"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,49 +117,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,19 +171,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,7 +195,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF52B869"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,211 +387,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -405,73 +453,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCD2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFACDDB7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -483,25 +531,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
+        <fgColor rgb="FFF2B8BE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -513,73 +543,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -591,36 +651,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB52331"/>
         <bgColor/>
       </patternFill>
@@ -633,37 +663,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -681,13 +681,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -705,37 +717,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -778,30 +802,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2442,7 +2442,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="13" t="str">
         <v>净卖: -4321.62万</v>
       </c>
       <c r="E2">
@@ -2457,41 +2457,41 @@
       <c r="H2">
         <v>-8.93</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="2">
         <v>-1.16</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="3">
         <v>1.68</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <v>3.44</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="8">
         <v>2.8</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="5">
         <v>8.43</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="6">
         <v>8.26</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="9">
         <v>1.85</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="10">
         <v>1.29</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="11">
         <v>6.24</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="12">
         <v>2.84</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="7">
         <v>4.86</v>
       </c>
-      <c r="T2" s="4">
-        <v>1.59</v>
+      <c r="T2" s="1">
+        <v>1.94</v>
       </c>
     </row>
     <row r="3">
@@ -2519,41 +2519,41 @@
       <c r="H3">
         <v>-1.63</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="24">
         <v>11.79</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="18">
         <v>22.97</v>
       </c>
       <c r="K3" s="25">
         <v>10.66</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="26">
         <v>4.1</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="19">
         <v>-0.44</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="20">
         <v>-3.41</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="21">
         <v>-6.38</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="22">
         <v>-7.69</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="14">
         <v>-6.64</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="15">
         <v>-6.72</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="17">
         <v>-6.81</v>
       </c>
-      <c r="T3" s="22">
-        <v>-4.02</v>
+      <c r="T3" s="16">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="4">
@@ -2566,7 +2566,7 @@
       <c r="C4" t="str">
         <v>001339</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="32" t="str">
         <v>净卖: -4.69万</v>
       </c>
       <c r="E4">
@@ -2581,41 +2581,41 @@
       <c r="H4">
         <v>4.9</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="28">
         <v>-2.37</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="37">
         <v>-5.33</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="34">
         <v>-8.23</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="29">
         <v>-8.82</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="30">
         <v>-8.07</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="35">
         <v>-5.42</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="38">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="36">
         <v>-7.04</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="39">
         <v>-9.46</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="31">
         <v>-8.86</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="33">
         <v>-9.81</v>
       </c>
-      <c r="T4" s="34">
-        <v>41.65</v>
+      <c r="T4" s="27">
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -2628,7 +2628,7 @@
       <c r="C5" t="str">
         <v>001339</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="42" t="str">
         <v>净卖: -7.88万</v>
       </c>
       <c r="E5">
@@ -2643,41 +2643,41 @@
       <c r="H5">
         <v>-6.54</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="43">
         <v>3.75</v>
       </c>
       <c r="J5" s="44">
         <v>0.58</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="45">
         <v>-0.08</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="47">
         <v>0.75</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="50">
         <v>3.65</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="46">
         <v>2.71</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="48">
         <v>1.88</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="40">
         <v>-0.77</v>
       </c>
       <c r="Q5" s="51">
         <v>-0.12</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="52">
         <v>-1.15</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="41">
         <v>2.13</v>
       </c>
-      <c r="T5" s="43">
-        <v>55.24</v>
+      <c r="T5" s="49">
+        <v>58.91</v>
       </c>
     </row>
     <row r="6">
@@ -2690,7 +2690,7 @@
       <c r="C6" t="str">
         <v>603516</v>
       </c>
-      <c r="D6" s="61" t="str">
+      <c r="D6" s="56" t="str">
         <v>净买: 5860.40万</v>
       </c>
       <c r="E6">
@@ -2708,38 +2708,38 @@
       <c r="I6" s="65">
         <v>9.46</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="57">
         <v>13.49</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="53">
         <v>20.29</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="58">
         <v>17.28</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="54">
         <v>29</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="62">
         <v>36.81</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="61">
         <v>45.23</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="63">
         <v>59.76</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="64">
         <v>43.78</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="59">
         <v>41.97</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="60">
         <v>40.57</v>
       </c>
-      <c r="T6" s="64">
-        <v>84.19</v>
+      <c r="T6" s="55">
+        <v>84.38</v>
       </c>
     </row>
     <row r="7">
@@ -2752,7 +2752,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="69" t="str">
         <v>净买: 6772.87万</v>
       </c>
       <c r="E7">
@@ -2767,41 +2767,41 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="70">
         <v>6.4</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="71">
         <v>17.05</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="72">
         <v>5.34</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="73">
         <v>4.01</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="66">
         <v>2.98</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="67">
         <v>4.47</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="74">
         <v>7.94</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="75">
         <v>-2.85</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="76">
         <v>-1.92</v>
       </c>
       <c r="R7" s="68">
         <v>4.08</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="77">
         <v>-6.33</v>
       </c>
-      <c r="T7" s="69">
-        <v>34.94</v>
+      <c r="T7" s="78">
+        <v>35.08</v>
       </c>
     </row>
     <row r="8">
@@ -2814,7 +2814,7 @@
       <c r="C8" t="str">
         <v>000718</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="82" t="str">
         <v>净买: 3497.63万</v>
       </c>
       <c r="E8">
@@ -2832,38 +2832,38 @@
       <c r="I8" s="86">
         <v>2.33</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="83">
         <v>1.74</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="91">
         <v>-5.52</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="87">
         <v>-2.33</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="88">
         <v>-12.21</v>
       </c>
-      <c r="N8" s="88">
+      <c r="N8" s="89">
         <v>-20.93</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="90">
         <v>-23.84</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="79">
         <v>-22.38</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="84">
         <v>-24.71</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="80">
         <v>-24.71</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="81">
         <v>-24.13</v>
       </c>
-      <c r="T8" s="83">
-        <v>-39.83</v>
+      <c r="T8" s="85">
+        <v>-39.24</v>
       </c>
     </row>
     <row r="9">
@@ -2876,7 +2876,7 @@
       <c r="C9" t="str">
         <v>002853</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="92" t="str">
         <v>净买: 1704.86万</v>
       </c>
       <c r="E9">
@@ -2891,41 +2891,41 @@
       <c r="H9">
         <v>-0.88</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="102">
         <v>9.12</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="103">
         <v>8.64</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="104">
         <v>12.55</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="93">
         <v>13.72</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="94">
         <v>11.34</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="99">
         <v>11.78</v>
       </c>
-      <c r="O9" s="103">
+      <c r="O9" s="95">
         <v>10.65</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="96">
         <v>14</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="100">
         <v>25.42</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="97">
         <v>32.36</v>
       </c>
-      <c r="S9" s="97">
+      <c r="S9" s="98">
         <v>29.18</v>
       </c>
-      <c r="T9" s="104">
-        <v>4.8</v>
+      <c r="T9" s="101">
+        <v>6.38</v>
       </c>
     </row>
     <row r="10">
@@ -2987,40 +2987,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="113">
+      <c r="I11" s="115">
         <v>75</v>
       </c>
       <c r="J11" s="116">
         <v>87.5</v>
       </c>
-      <c r="K11" s="112">
+      <c r="K11" s="108">
         <v>62.5</v>
       </c>
-      <c r="L11" s="105">
+      <c r="L11" s="111">
         <v>75</v>
       </c>
-      <c r="M11" s="110">
+      <c r="M11" s="106">
         <v>62.5</v>
       </c>
-      <c r="N11" s="106">
+      <c r="N11" s="112">
         <v>62.5</v>
       </c>
-      <c r="O11" s="111">
+      <c r="O11" s="113">
         <v>62.5</v>
       </c>
-      <c r="P11" s="107">
+      <c r="P11" s="109">
         <v>37.5</v>
       </c>
-      <c r="Q11" s="114">
+      <c r="Q11" s="107">
         <v>37.5</v>
       </c>
-      <c r="R11" s="108">
+      <c r="R11" s="110">
         <v>50</v>
       </c>
-      <c r="S11" s="109">
+      <c r="S11" s="105">
         <v>50</v>
       </c>
-      <c r="T11" s="115">
+      <c r="T11" s="114">
         <v>75</v>
       </c>
     </row>
@@ -3035,41 +3035,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="120">
+      <c r="I12" s="119">
         <v>4.91</v>
       </c>
-      <c r="J12" s="121">
+      <c r="J12" s="128">
         <v>7.6</v>
       </c>
-      <c r="K12" s="118">
+      <c r="K12" s="125">
         <v>4.81</v>
       </c>
-      <c r="L12" s="128">
+      <c r="L12" s="121">
         <v>3.94</v>
       </c>
-      <c r="M12" s="123">
+      <c r="M12" s="122">
         <v>4.33</v>
       </c>
-      <c r="N12" s="124">
+      <c r="N12" s="117">
         <v>4.28</v>
       </c>
-      <c r="O12" s="122">
+      <c r="O12" s="126">
         <v>3.88</v>
       </c>
-      <c r="P12" s="125">
+      <c r="P12" s="127">
         <v>4.29</v>
       </c>
-      <c r="Q12" s="117">
+      <c r="Q12" s="123">
         <v>4.07</v>
       </c>
-      <c r="R12" s="126">
+      <c r="R12" s="118">
         <v>4.98</v>
       </c>
-      <c r="S12" s="127">
+      <c r="S12" s="120">
         <v>3.71</v>
       </c>
-      <c r="T12" s="119">
-        <v>22.32</v>
+      <c r="T12" s="124">
+        <v>23.64</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/轮回666/index.xlsx
+++ b/youzi/轮回666/index.xlsx
@@ -39,61 +39,625 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCDEAD3"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3BBC0"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,559 +669,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -669,6 +699,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
@@ -681,72 +717,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -759,13 +747,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2442,7 +2442,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="8" t="str">
         <v>净卖: -4321.62万</v>
       </c>
       <c r="E2">
@@ -2457,41 +2457,41 @@
       <c r="H2">
         <v>-8.93</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>-1.16</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="12">
         <v>1.68</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="2">
         <v>3.44</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="9">
         <v>2.8</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="13">
         <v>8.43</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="3">
         <v>8.26</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="4">
         <v>1.85</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="5">
         <v>1.29</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="10">
         <v>6.24</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="6">
         <v>2.84</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="11">
         <v>4.86</v>
       </c>
-      <c r="T2" s="1">
-        <v>1.94</v>
+      <c r="T2" s="7">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="3">
@@ -2504,7 +2504,7 @@
       <c r="C3" t="str">
         <v>600250</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 7132.41万</v>
       </c>
       <c r="E3">
@@ -2519,41 +2519,41 @@
       <c r="H3">
         <v>-1.63</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="17">
         <v>11.79</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="20">
         <v>22.97</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="14">
         <v>10.66</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="15">
         <v>4.1</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="18">
         <v>-0.44</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="21">
         <v>-3.41</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="19">
         <v>-6.38</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="25">
         <v>-7.69</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="22">
         <v>-6.64</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="16">
         <v>-6.72</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="23">
         <v>-6.81</v>
       </c>
-      <c r="T3" s="16">
-        <v>-3.32</v>
+      <c r="T3" s="24">
+        <v>-6.72</v>
       </c>
     </row>
     <row r="4">
@@ -2566,7 +2566,7 @@
       <c r="C4" t="str">
         <v>001339</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="31" t="str">
         <v>净卖: -4.69万</v>
       </c>
       <c r="E4">
@@ -2581,41 +2581,41 @@
       <c r="H4">
         <v>4.9</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="32">
         <v>-2.37</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="33">
         <v>-5.33</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="39">
         <v>-8.23</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="37">
         <v>-8.82</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="29">
         <v>-8.07</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="34">
         <v>-5.42</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="27">
         <v>-6.28</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="38">
         <v>-7.04</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="35">
         <v>-9.46</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="36">
         <v>-8.86</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="30">
         <v>-9.81</v>
       </c>
-      <c r="T4" s="27">
-        <v>45</v>
+      <c r="T4" s="28">
+        <v>54.39</v>
       </c>
     </row>
     <row r="5">
@@ -2628,7 +2628,7 @@
       <c r="C5" t="str">
         <v>001339</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -7.88万</v>
       </c>
       <c r="E5">
@@ -2643,41 +2643,41 @@
       <c r="H5">
         <v>-6.54</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="49">
         <v>3.75</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="52">
         <v>0.58</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="44">
         <v>-0.08</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="40">
         <v>0.75</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="45">
         <v>3.65</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="41">
         <v>2.71</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="47">
         <v>1.88</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="50">
         <v>-0.77</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="48">
         <v>-0.12</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="42">
         <v>-1.15</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="43">
         <v>2.13</v>
       </c>
-      <c r="T5" s="49">
-        <v>58.91</v>
+      <c r="T5" s="51">
+        <v>69.2</v>
       </c>
     </row>
     <row r="6">
@@ -2690,7 +2690,7 @@
       <c r="C6" t="str">
         <v>603516</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="61" t="str">
         <v>净买: 5860.40万</v>
       </c>
       <c r="E6">
@@ -2705,41 +2705,41 @@
       <c r="H6">
         <v>0.49</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="62">
         <v>9.46</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="55">
         <v>13.49</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="63">
         <v>20.29</v>
       </c>
       <c r="L6" s="58">
         <v>17.28</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="64">
         <v>29</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="65">
         <v>36.81</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="57">
         <v>45.23</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="59">
         <v>59.76</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="53">
         <v>43.78</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="54">
         <v>41.97</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="56">
         <v>40.57</v>
       </c>
-      <c r="T6" s="55">
-        <v>84.38</v>
+      <c r="T6" s="60">
+        <v>81.19</v>
       </c>
     </row>
     <row r="7">
@@ -2752,7 +2752,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="77" t="str">
         <v>净买: 6772.87万</v>
       </c>
       <c r="E7">
@@ -2767,41 +2767,41 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="78">
         <v>6.4</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="66">
         <v>17.05</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="70">
         <v>5.34</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="74">
         <v>4.01</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="71">
         <v>2.98</v>
       </c>
       <c r="N7" s="67">
         <v>4.47</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="75">
         <v>7.94</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="76">
         <v>-2.85</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="72">
         <v>-1.92</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="73">
         <v>4.08</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="68">
         <v>-6.33</v>
       </c>
-      <c r="T7" s="78">
-        <v>35.08</v>
+      <c r="T7" s="69">
+        <v>32.74</v>
       </c>
     </row>
     <row r="8">
@@ -2814,7 +2814,7 @@
       <c r="C8" t="str">
         <v>000718</v>
       </c>
-      <c r="D8" s="82" t="str">
+      <c r="D8" s="85" t="str">
         <v>净买: 3497.63万</v>
       </c>
       <c r="E8">
@@ -2829,40 +2829,40 @@
       <c r="H8">
         <v>3.93</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="81">
         <v>2.33</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="91">
         <v>1.74</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="88">
         <v>-5.52</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="86">
         <v>-2.33</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="89">
         <v>-12.21</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="82">
         <v>-20.93</v>
       </c>
-      <c r="O8" s="90">
+      <c r="O8" s="83">
         <v>-23.84</v>
       </c>
       <c r="P8" s="79">
         <v>-22.38</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="87">
         <v>-24.71</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="84">
         <v>-24.71</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="80">
         <v>-24.13</v>
       </c>
-      <c r="T8" s="85">
+      <c r="T8" s="90">
         <v>-39.24</v>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       <c r="C9" t="str">
         <v>002853</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="93" t="str">
         <v>净买: 1704.86万</v>
       </c>
       <c r="E9">
@@ -2891,41 +2891,41 @@
       <c r="H9">
         <v>-0.88</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="98">
         <v>9.12</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="94">
         <v>8.64</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="95">
         <v>12.55</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="101">
         <v>13.72</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="92">
         <v>11.34</v>
       </c>
       <c r="N9" s="99">
         <v>11.78</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="100">
         <v>10.65</v>
       </c>
       <c r="P9" s="96">
         <v>14</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="102">
         <v>25.42</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="103">
         <v>32.36</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="97">
         <v>29.18</v>
       </c>
-      <c r="T9" s="101">
-        <v>6.38</v>
+      <c r="T9" s="104">
+        <v>4.72</v>
       </c>
     </row>
     <row r="10">
@@ -2987,41 +2987,41 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="115">
+      <c r="I11" s="111">
         <v>75</v>
       </c>
-      <c r="J11" s="116">
+      <c r="J11" s="106">
         <v>87.5</v>
       </c>
-      <c r="K11" s="108">
+      <c r="K11" s="112">
         <v>62.5</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="107">
         <v>75</v>
       </c>
-      <c r="M11" s="106">
+      <c r="M11" s="108">
         <v>62.5</v>
       </c>
-      <c r="N11" s="112">
+      <c r="N11" s="116">
         <v>62.5</v>
       </c>
-      <c r="O11" s="113">
+      <c r="O11" s="109">
         <v>62.5</v>
       </c>
-      <c r="P11" s="109">
+      <c r="P11" s="113">
         <v>37.5</v>
       </c>
-      <c r="Q11" s="107">
+      <c r="Q11" s="114">
         <v>37.5</v>
       </c>
-      <c r="R11" s="110">
+      <c r="R11" s="115">
         <v>50</v>
       </c>
-      <c r="S11" s="105">
+      <c r="S11" s="110">
         <v>50</v>
       </c>
-      <c r="T11" s="114">
-        <v>75</v>
+      <c r="T11" s="105">
+        <v>62.5</v>
       </c>
     </row>
     <row r="12">
@@ -3035,41 +3035,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="119">
+      <c r="I12" s="120">
         <v>4.91</v>
       </c>
-      <c r="J12" s="128">
+      <c r="J12" s="121">
         <v>7.6</v>
       </c>
-      <c r="K12" s="125">
+      <c r="K12" s="128">
         <v>4.81</v>
       </c>
-      <c r="L12" s="121">
+      <c r="L12" s="122">
         <v>3.94</v>
       </c>
-      <c r="M12" s="122">
+      <c r="M12" s="123">
         <v>4.33</v>
       </c>
-      <c r="N12" s="117">
+      <c r="N12" s="125">
         <v>4.28</v>
       </c>
       <c r="O12" s="126">
         <v>3.88</v>
       </c>
-      <c r="P12" s="127">
+      <c r="P12" s="117">
         <v>4.29</v>
       </c>
-      <c r="Q12" s="123">
+      <c r="Q12" s="127">
         <v>4.07</v>
       </c>
-      <c r="R12" s="118">
+      <c r="R12" s="124">
         <v>4.98</v>
       </c>
-      <c r="S12" s="120">
+      <c r="S12" s="118">
         <v>3.71</v>
       </c>
-      <c r="T12" s="124">
-        <v>23.64</v>
+      <c r="T12" s="119">
+        <v>24.33</v>
       </c>
     </row>
   </sheetData>
